--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\acmp\excelbibltest\ExcelBiblT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59B51CF-2D84-4226-9C3C-87E0DCB2D742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA6CA84-17C5-4F2F-A12D-125C54FA9622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29892" yWindow="-108" windowWidth="30000" windowHeight="17496" activeTab="1" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
+    <workbookView xWindow="828" yWindow="-108" windowWidth="30000" windowHeight="17496" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Параметры" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="115">
   <si>
     <t>Название</t>
   </si>
@@ -370,20 +370,31 @@
     <t>Псевдонимы</t>
   </si>
   <si>
-    <t>нет</t>
-  </si>
-  <si>
     <t>(Расш.) Кол-во дисциплин в УП</t>
   </si>
   <si>
     <t>(Расш.) Общее колв-о ЗЕ в УП</t>
+  </si>
+  <si>
+    <t>Формула расчёта весов рёбер</t>
+  </si>
+  <si>
+    <t>((L + R) / 2) * K</t>
+  </si>
+  <si>
+    <t>В формуле расчёта весов ниже следующая легенда:
+L - ЗЕ левой вершины,
+ R - ЗЕ правой вершины,
+A - суммарное колв-о ЗЕ,
+N - суммарное кол-во дисциплин,
+K - мощность пересечения по компетенциям</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -402,6 +413,22 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -472,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -507,6 +534,14 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -821,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049FB1B4-2A61-4643-8816-8B76EC36FD4B}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.09765625" customWidth="1"/>
@@ -883,7 +918,7 @@
         <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -974,7 +1009,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>78</v>
       </c>
@@ -982,7 +1017,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -990,7 +1025,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -998,7 +1033,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -1006,7 +1041,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>95</v>
       </c>
@@ -1014,7 +1049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>108</v>
       </c>
@@ -1022,7 +1057,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>106</v>
       </c>
@@ -1030,15 +1065,32 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>101</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
     </row>
+    <row r="25" spans="1:5" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:A3"/>
@@ -1046,6 +1098,7 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -1095,18 +1148,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\acmp\excelbibltest\ExcelBiblT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA6CA84-17C5-4F2F-A12D-125C54FA9622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4362DBD8-F429-4E2F-A04D-C37B334CDDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="828" yWindow="-108" windowWidth="30000" windowHeight="17496" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
   </bookViews>
